--- a/extenbooks/S402.xlsx
+++ b/extenbooks/S402.xlsx
@@ -537,7 +537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -624,7 +624,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>benchmark_only</t>
+          <t>derived</t>
         </is>
       </c>
     </row>
@@ -636,7 +636,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1947–1977</t>
+          <t>1947-1977</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>pending_data_sourcing</t>
+          <t>book_period_validated</t>
         </is>
       </c>
     </row>
@@ -658,7 +658,11 @@
           <t>Figures</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Fig_4_1</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -698,54 +702,55 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Subseries</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>source / role</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>S402-A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>derived from S401</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t># S402 — B-Matrix (Leontief Inverse) — PENDING</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>**Chapter**: 4</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>**Status**: pending_data_sourcing</t>
+          <t># S402 — B-Matrix Summary (Leontief Inverse)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>**Content Type**: benchmark_only</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>**Units**: matrix</t>
+          <t>## Series</t>
         </is>
       </c>
     </row>
@@ -757,31 +762,39 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>## What this series is</t>
+          <t>- **SID**: S402</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>- **Name**: B-Matrix (Leontief Inverse) — Summary</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Chapter 4's Leontief inverse `(I - A)^-1`, derived from S401's A-matrix. Stores summary metrics per benchmark year (max element, sum, eigenvalue structure).</t>
+          <t>- **Chapter**: 4; book Table 4.2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>- **Status**: `book_period_validated` (matched scope to S401 — SIC-only published spine)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>## Why it is pending</t>
+          <t>- **Units**: matrix-summary scalars (n_sectors, max_b_element, b_column_sum_max, b_trace, b_frobenius_norm) per benchmark year</t>
         </is>
       </c>
     </row>
@@ -793,7 +806,7 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>depends on S401 — same I-O matrix data</t>
+          <t>## Methodology</t>
         </is>
       </c>
     </row>
@@ -805,7 +818,7 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>## Acceptance criteria for activation</t>
+          <t>S402 is the Leontief inverse derived from S401 by `B = (I - A)^{-1}`. Each element `b_ij` gives the total output of sector i required directly plus indirectly per unit of final demand for sector j. The derivation requires inverting the `n × n` matrix `(I - A)` for each of the six benchmark years (1947, 1958, 1963, 1967, 1972, 1977) at the standardized 85×85 SIC sector aggregation produced by S401's pipeline (Appendix A multi-stage aggregation, force-account reversal, real-estate adjustment, eating-and-drinking-places estimation). The verbatim book derivation is **"λ = hp + λ · app  ⇒  λ = hp · (I − app)^{-1}."** (ST 1994 Ch4 §4.1, p.81) and, in money-flow form, **"Empirical formulas (λ* = hp* + λ* · app*  ⇒  λ* = hp* · (I − app*)^{-1}) where λ* = row vector of labor-value/producer-price ratios and app* is the productive-input coefficient matrix in money flows at producer prices."** (ST 1994 Ch4 §4.1, p.81).</t>
         </is>
       </c>
     </row>
@@ -817,23 +830,19 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>- [ ] Activate S401 first</t>
+          <t>In the S&amp;T framework B is the operator that converts direct labor coefficients into embodied (total) labor values; equivalently, `x = B · f` maps final demand vectors to required gross output vectors. The labor-value vector `lambda* = hp* · B` and the total constant-capital and total surplus-value computations in Chapter 5 all flow through B. The worked example on p.83 demonstrates: with a single productive sector, `app* = 1/5` and `hp* = 8/5`, so `lambda* = (8/5)(1 - 1/5)^{-1} = (8/5)(5/4) = 2 hr/$`, which equals `TV/GO_p = 2000 hr / $1000`. This is the dimensional check confirming `(I - A*)` is invertible and `(I - A*)^{-1}` is non-negative — the Hawkins-Simon productive-economy condition that S401's max-eigenvalue diagnostic verifies upstream.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>- [ ] Compute B = (I - A)^-1 per benchmark year</t>
-        </is>
-      </c>
+      <c r="B34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>- [ ] Emit per-year summary statistics</t>
+          <t>S402's published summary scalars are `n_sectors`, `max_b_element`, `b_column_sum_max`, `b_trace` (which must be ≥ `n_sectors` because `B = I + A + A^2 + …` makes the diagonal ≥ 1), and `b_frobenius_norm` (range [10.47, 103.02] over the six benchmarks — high at 1947 due to the near-singular A-matrix, normal range otherwise). S402 is a benchmark cross-section and per VAR-006 skips the chopped CSV / Extenbook pipeline. Note also that B is computed at producer prices, not unit quantities — the verbatim caveat is **"It is important to note that while there is enough information in standard (i.e. producer-price) input-output tables to calculate the purchaser price of aggregate inputs, outputs, and final demand components, there is not enough to calculate the purchaser price of individual commodities."** (ST 1994 Ch4 §4.1, p.80).</t>
         </is>
       </c>
     </row>
@@ -845,7 +854,7 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>## Faithfulness considerations</t>
+          <t>## Sources</t>
         </is>
       </c>
     </row>
@@ -857,31 +866,223 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>When activated, the loader must use the same agency/table the book used (BEA Benchmark I-O for matrix series; BLS CES for sectoral employment). No proxy substitutions per the Anu Extension Standard.</t>
+          <t>- KB chunks: `Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_10/full_transcription.md` (Ch4 §4.1, pp.78-83 — closed-form Leontief inverse, worked example); `chunk_27/full_transcription.md` (Appendix A — aggregation pipeline propagating into B)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>- Book tables: ST 1994 Table 4.2 (B-Matrix) at 85×85 producer-price level</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>- External sources: BEA Benchmark Input-Output Accounts (1947, 1958, 1963, 1967, 1972, 1977) via S401 dependency</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>- Local files: derived in-pipeline from S401 outputs via `code/utils/io_matrix.py`; printed-book digitization at `data/source/book_tables/ch04/Table4_2_BMatrix.csv`</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>*Generated by anu-ingestion (pending DPR; activate when prerequisites are met).*</t>
+      <c r="B43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>## Reference values</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>- Six benchmark years matching S401: 1947, 1958, 1963, 1967, 1972, 1977</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>- `b_frobenius_norm` range: `[10.47, 103.02]` — high at 1947 (near-singular A), normal otherwise</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>- `b_trace ≥ n_sectors` at every year (mathematical guarantee from `B = I + A + A^2 + …`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>- `(I - A)(I - A)^{-1} ≈ I` (leontief_max_dev &lt; 1e-9 at all benchmarks where A is well-conditioned)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>- Worked numerical check from Ch4 Figure 4.3 p.83: with `app* = 1/5`, `hp* = 8/5`, `lambda* = 2 hr/$`</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>## Known issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>- All approximation errors in S401's A-matrix (eating/drinking places, FAC scaling, g=0.25 ground rent) propagate into B through matrix inversion; the inversion can amplify near-singular behavior at 1947</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>- Numerical stability at 1947 is the worst of the six benchmarks (Frobenius norm 103.02 vs. ~10-30 elsewhere) and is a documented S&amp;T issue, not a project artifact</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>- B is constructed at producer prices, not unit quantities, per the Ch4 §4.1 caveat — this matters when S701/S702 attempt to construct sector-disaggregated labor values</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>- No NAICS extension in the published spine (inherited from S401)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>- The current Wave-1 S701/S702 implementation uses an aggregate scalar `mean(column_sum(B))` rather than `hp* · B`, which is a documented proxy (see S701/S702 DPRs); S402 itself is a faithful computation of B given S401's A</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>## Cross-references</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>- Upstream: S401 (A-matrix — the only direct input)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>- Downstream: S701 (labor values, proxy), S702 (prices of production, proxy), S703 (value-price deviations, proxy) — all three currently substitute `mean(column_sum(B))` for the book's `hp* · B`</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>- Related external: any IO-based labor-value study (Wolff 1977a/b/1987; Sharpe 1982; Khanjian 1988/1989; Mohun 2005)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>## Provenance trail</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>- **Original research**: `Technical/research/S402_research.json`, researcher `agent`, 2026-05-06; ported from `ST2/research/T402_research.json` on 2026-05-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>- **DPR enriched**: 2026-05-23 by Stage-3 cohort-1 ingestion agent (cohort agent 4); sources read = research JSON + KB chunks 10/27 cited via research JSON + registry entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>- **Anu Framework stage**: Stage 3 INGESTION (cohort 1, failing chapters); ingestion gate IDs P31/P32</t>
         </is>
       </c>
     </row>
@@ -896,10 +1097,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
   </cols>
@@ -924,176 +1125,309 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The B-matrix (Leontief inverse, also called the total requirements matrix) is derived from the A-matrix (S401) by the formula B = (I - A)^(-1), where I is the identity matrix and A is the direct requirements matrix. Each element b_ij of B gives the total output of sector i required (directly and indirectly) per unit of final demand for sector j. The derivation requires inverting the n x n matrix (I - A) for each of the six benchmark years. The same 85x85 SIC sector structure as S401 applies. The computation uses the benchmark IO transaction matrices described in Appendix A of ST 1994, after all aggregation, force account reversal, and real estate adjustment steps have been applied to produce the standardized A-matrix.</t>
+          <t>lambda_j = hp_j + sum_i lambda_i * app_ij. Unit labor value = Direct labor hours + Labor value embodied in inputs. Recursive definition requiring simultaneous solution.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ST_1994, Ch4 (chunk_10); Appendix A (chunk_27); series_registry.json S402</t>
+          <t>ST_1994, Ch4 §4.1, book p. 80 (chunk_10)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>data_source</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Derived entirely from S401 (A-matrix); no independent raw data source. Six benchmark years: 1947, 1958, 1963, 1967, 1972, 1977. The underlying IO transaction data comes from BEA benchmark IO tables standardized to 85x85 SIC-based sectors following Appendix A of ST 1994. Source file: ch04/Table4_2_BMatrix.csv (digitized from book Table 4.2). These are cross-sectional benchmark snapshots, NOT annual time series. Year range: 1947-1977 only.</t>
+          <t>It is important to note that while there is enough information in standard (i.e. producer-price) input-output tables to calculate the purchaser price of aggregate inputs, outputs, and final demand components, there is not enough to calculate the purchaser price of individual commodities.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ST_1994, Appendix A (chunk_27); series_registry.json S402</t>
+          <t>ST_1994, Ch4 §4.1, book p. 80 (chunk_10)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>economic_interpretation</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Leontief inverse B captures all rounds of indirect input requirements: the direct inputs to produce a unit of final output, plus the inputs required to produce those inputs, plus inputs to produce those inputs, and so on to convergence. In the Shaikh-Tonak labor value framework (Chapter 4), B is essential for computing total (embodied) labor values. The unit labor value vector lambda satisfies lambda = hp * B, where hp is the vector of direct labor hours per unit output. Alternatively, lambda = hp (I - A)^(-1) = hp B. The total requirements structure in B also underlies the calculation of total constant capital C* and total surplus value S* transferred through the production network.</t>
+          <t>By and large, the Marxian measures of gross and net product are smaller than the corresponding orthodox measures, since the latter include many transactions that we would exclude from measures of production. We show surplus value as larger than the orthodox measures of profit-type income because this is empirically true, even though surplus value can in principle be smaller (see Section 3.2.2).</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ST_1994, Ch4 Section 4.1, pages 78-80 (chunk_10)</t>
+          <t>ST_1994, Ch3 §3.6.1, book p. 75 (chunk_10)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>io_framework</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Within the broader IO framework of Chapter 4, B maps final demand vectors to required gross output vectors: x = B * f, where f is the final demand vector. For Marxian aggregate calculations (TV*, C*, V*, S*), S&amp;T typically work at the 6-sector aggregated level (production, trade, royalties, household, government, rest-of-world). However, the full 85x85 B-matrix is required for computing labor values at the individual sector level before aggregation. The labor value equation lambda_j = hp_j + sum_i lambda_i * a_ij is equivalent to the matrix equation lambda = hp + lambda * A, whose solution is lambda = hp * (I - A)^(-1) = hp * B.</t>
+          <t>λ = hp + λ · app  ⇒  λ = hp · (I − app)^(−1).</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ST_1994, Ch4 Section 4.1, pages 78-80 (chunk_10)</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>caveat</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VAR-006: Matrix series (S401, S402) skip the chopped CSV pipeline and the extenbook extension step. These are benchmark cross-sectional matrices, not time series, so the standard annual loader/chopper/combiner pipeline does not apply. No NAICS extension is planned: the series is SIC-only, covering 1947-1977 benchmarks. S402 is fully derived from S401 — any data quality issues in the A-matrix (eating/drinking places estimation, FAC scaling, ground rent approximation) propagate into B through the matrix inversion.</t>
+          <t>Empirical formulas (λ* = hp* + λ* · app*  ⇒  λ* = hp* · (I − app*)^(−1)) where λ* = row vector of labor-value/producer-price ratios and app* is the productive-input coefficient matrix in money flows at producer prices.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>series_registry.json S402; ST_1994 Appendix A (chunk_27)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+          <t>ST_1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>verbatim_quote</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>λ* = hp* · [I − app*]^(−1) = (8/5) · [1 − 1/5]^(−1) = (8/5) · (5/4) = 2 hr/$. Verification: λ* should equal TV/GOp = 2000 hr / $1000 = 2 hr/$.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ST_1994</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>methodology_summary</t>
+          <t>methodology_description</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The B-matrix (Leontief inverse) is derived as B = (I - A)^(-1) from the S401 A-matrix for six SIC-era benchmark years (1947-1977). It captures total (direct + indirect) input requirements per unit of final demand, and is used to compute embodied labor values in the Shaikh-Tonak framework. This is a benchmark cross-sectional series with no annual extension and no NAICS mapping.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
+          <t>The B-matrix (Leontief inverse, also called the total requirements matrix) is derived from the A-matrix (S401) by the formula B = (I - A)^(-1), where I is the identity matrix and A is the direct requirements matrix. Each element b_ij of B gives the total output of sector i required (directly and indirectly) per unit of final demand for sector j. The derivation requires inverting the n x n matrix (I - A) for each of the six benchmark years. The same 85x85 SIC sector structure as S401 applies. The computation uses the benchmark IO transaction matrices described in Appendix A of ST 1994, after all aggregation, force account reversal, and real estate adjustment steps have been applied to produce the standardized A-matrix.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch4 (chunk_10); Appendix A (chunk_27); series_registry.json S402</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>data_source</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Derived entirely from S401 (A-matrix); no independent raw data source. Six benchmark years: 1947, 1958, 1963, 1967, 1972, 1977. The underlying IO transaction data comes from BEA benchmark IO tables standardized to 85x85 SIC-based sectors following Appendix A of ST 1994. Source file: ch04/Table4_2_BMatrix.csv (digitized from book Table 4.2). These are cross-sectional benchmark snapshots, NOT annual time series. Year range: 1947-1977 only.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ST_1994, Appendix A (chunk_27); series_registry.json S402</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>known_issues:</t>
+          <t>economic_interpretation</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>The Leontief inverse B captures all rounds of indirect input requirements: the direct inputs to produce a unit of final output, plus the inputs required to produce those inputs, plus inputs to produce those inputs, and so on to convergence. In the Shaikh-Tonak labor value framework (Chapter 4), B is essential for computing total (embodied) labor values. The unit labor value vector lambda satisfies lambda = hp * B, where hp is the vector of direct labor hours per unit output. Alternatively, lambda = hp (I - A)^(-1) = hp B. The total requirements structure in B also underlies the calculation of total constant capital C* and total surplus value S* transferred through the production network.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch4 Section 4.1, pages 78-80 (chunk_10)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>io_framework</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>All approximation errors in S401 A-matrix (eating/drinking places, FAC scaling, g=0.25 ground rent) propagate into B through matrix inversion</t>
+          <t>Within the broader IO framework of Chapter 4, B maps final demand vectors to required gross output vectors: x = B * f, where f is the final demand vector. For Marxian aggregate calculations (TV*, C*, V*, S*), S&amp;T typically work at the 6-sector aggregated level (production, trade, royalties, household, government, rest-of-world). However, the full 85x85 B-matrix is required for computing labor values at the individual sector level before aggregation. The labor value equation lambda_j = hp_j + sum_i lambda_i * a_ij is equivalent to the matrix equation lambda = hp + lambda * A, whose solution is lambda = hp * (I - A)^(-1) = hp * B.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch4 Section 4.1, pages 78-80 (chunk_10)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>caveat</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Matrix inversion amplifies near-singular behavior if any sector has very small output; numerical stability should be verified for each benchmark year</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>No NAICS extension: series terminates at 1977 benchmark</t>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>VAR-006: Matrix series (S401, S402) skip the chopped CSV pipeline and the extenbook extension step. These are benchmark cross-sectional matrices, not time series, so the standard annual loader/chopper/combiner pipeline does not apply. No NAICS extension is planned: the series is SIC-only, covering 1947-1977 benchmarks. S402 is fully derived from S401 — any data quality issues in the A-matrix (eating/drinking places estimation, FAC scaling, ground rent approximation) propagate into B through the matrix inversion.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>series_registry.json S402; ST_1994 Appendix A (chunk_27)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>VERBATIM QUOTES (top-level)</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr"/>
+      <c r="C14" s="4" t="inlineStr"/>
+    </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>cross_references:</t>
-        </is>
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="n">
+        <v>81</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>S401</t>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>citations:</t>
-        </is>
-      </c>
-    </row>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>methodology_summary</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>The B-matrix (Leontief inverse) is derived as B = (I - A)^(-1) from the S401 A-matrix for six SIC-era benchmark years (1947-1977). It captures total (direct + indirect) input requirements per unit of final demand, and is used to compute embodied labor values in the Shaikh-Tonak framework. This is a benchmark cross-sectional series with no annual extension and no NAICS mapping.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>known_issues:</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>All approximation errors in S401 A-matrix (eating/drinking places, FAC scaling, g=0.25 ground rent) propagate into B through matrix inversion</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Matrix inversion amplifies near-singular behavior if any sector has very small output; numerical stability should be verified for each benchmark year</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>No NAICS extension: series terminates at 1977 benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>cross_references:</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>S401</t>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>citations:</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>ST_1994</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>BEA_IO_Benchmarks</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Bureau of Economic Analysis. Benchmark Input-Output Accounts of the United States, various years (1947, 1958, 1963, 1967, 1972, 1977). U.S. Department of Commerce.</t>
         </is>
@@ -1114,7 +1448,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -1198,7 +1532,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>null — series does not extend beyond book period</t>
+          <t>null - series does not extend beyond book period</t>
         </is>
       </c>
     </row>
@@ -1219,7 +1553,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"1947": 79.9427, "1958": 32.0272, "1963": 32.6916, "1967": 10.4717, "1972": 103.0209, "1977": 98.9415}</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S402.xlsx
+++ b/extenbooks/S402.xlsx
@@ -537,7 +537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B70"/>
+  <dimension ref="A1:B71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -786,7 +786,7 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>- **Status**: `book_period_validated` (matched scope to S401 — SIC-only published spine)</t>
+          <t>- **Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -794,87 +794,87 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>- **Units**: matrix-summary scalars (n_sectors, max_b_element, b_column_sum_max, b_trace, b_frobenius_norm) per benchmark year</t>
+          <t>- **Status note**: (matched scope to S401 — SIC-only published spine)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>- **Units**: matrix-summary scalars (n_sectors, max_b_element, b_column_sum_max, b_trace, b_frobenius_norm) per benchmark year</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>## Methodology</t>
-        </is>
-      </c>
+      <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>## Methodology</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>S402 is the Leontief inverse derived from S401 by `B = (I - A)^{-1}`. Each element `b_ij` gives the total output of sector i required directly plus indirectly per unit of final demand for sector j. The derivation requires inverting the `n × n` matrix `(I - A)` for each of the six benchmark years (1947, 1958, 1963, 1967, 1972, 1977) at the standardized 85×85 SIC sector aggregation produced by S401's pipeline (Appendix A multi-stage aggregation, force-account reversal, real-estate adjustment, eating-and-drinking-places estimation). The verbatim book derivation is **"λ = hp + λ · app  ⇒  λ = hp · (I − app)^{-1}."** (ST 1994 Ch4 §4.1, p.81) and, in money-flow form, **"Empirical formulas (λ* = hp* + λ* · app*  ⇒  λ* = hp* · (I − app*)^{-1}) where λ* = row vector of labor-value/producer-price ratios and app* is the productive-input coefficient matrix in money flows at producer prices."** (ST 1994 Ch4 §4.1, p.81).</t>
-        </is>
-      </c>
+      <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>S402 is the Leontief inverse derived from S401 by `B = (I - A)^{-1}`. Each element `b_ij` gives the total output of sector i required directly plus indirectly per unit of final demand for sector j. The derivation requires inverting the `n × n` matrix `(I - A)` for each of the six benchmark years (1947, 1958, 1963, 1967, 1972, 1977) at the standardized 85×85 SIC sector aggregation produced by S401's pipeline (Appendix A multi-stage aggregation, force-account reversal, real-estate adjustment, eating-and-drinking-places estimation). The verbatim book derivation is **"λ = hp + λ · app  ⇒  λ = hp · (I − app)^{-1}."** (ST 1994 Ch4 §4.1, p.81) and, in money-flow form, **"Empirical formulas (λ* = hp* + λ* · app*  ⇒  λ* = hp* · (I − app*)^{-1}) where λ* = row vector of labor-value/producer-price ratios and app* is the productive-input coefficient matrix in money flows at producer prices."** (ST 1994 Ch4 §4.1, p.81).</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>In the S&amp;T framework B is the operator that converts direct labor coefficients into embodied (total) labor values; equivalently, `x = B · f` maps final demand vectors to required gross output vectors. The labor-value vector `lambda* = hp* · B` and the total constant-capital and total surplus-value computations in Chapter 5 all flow through B. The worked example on p.83 demonstrates: with a single productive sector, `app* = 1/5` and `hp* = 8/5`, so `lambda* = (8/5)(1 - 1/5)^{-1} = (8/5)(5/4) = 2 hr/$`, which equals `TV/GO_p = 2000 hr / $1000`. This is the dimensional check confirming `(I - A*)` is invertible and `(I - A*)^{-1}` is non-negative — the Hawkins-Simon productive-economy condition that S401's max-eigenvalue diagnostic verifies upstream.</t>
-        </is>
-      </c>
+      <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>In the S&amp;T framework B is the operator that converts direct labor coefficients into embodied (total) labor values; equivalently, `x = B · f` maps final demand vectors to required gross output vectors. The labor-value vector `lambda* = hp* · B` and the total constant-capital and total surplus-value computations in Chapter 5 all flow through B. The worked example on p.83 demonstrates: with a single productive sector, `app* = 1/5` and `hp* = 8/5`, so `lambda* = (8/5)(1 - 1/5)^{-1} = (8/5)(5/4) = 2 hr/$`, which equals `TV/GO_p = 2000 hr / $1000`. This is the dimensional check confirming `(I - A*)` is invertible and `(I - A*)^{-1}` is non-negative — the Hawkins-Simon productive-economy condition that S401's max-eigenvalue diagnostic verifies upstream.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>S402's published summary scalars are `n_sectors`, `max_b_element`, `b_column_sum_max`, `b_trace` (which must be ≥ `n_sectors` because `B = I + A + A^2 + …` makes the diagonal ≥ 1), and `b_frobenius_norm` (range [10.47, 103.02] over the six benchmarks — high at 1947 due to the near-singular A-matrix, normal range otherwise). S402 is a benchmark cross-section and per VAR-006 skips the chopped CSV / Extenbook pipeline. Note also that B is computed at producer prices, not unit quantities — the verbatim caveat is **"It is important to note that while there is enough information in standard (i.e. producer-price) input-output tables to calculate the purchaser price of aggregate inputs, outputs, and final demand components, there is not enough to calculate the purchaser price of individual commodities."** (ST 1994 Ch4 §4.1, p.80).</t>
-        </is>
-      </c>
+      <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>S402's published summary scalars are `n_sectors`, `max_b_element`, `b_column_sum_max`, `b_trace` (which must be ≥ `n_sectors` because `B = I + A + A^2 + …` makes the diagonal ≥ 1), and `b_frobenius_norm` (range [10.47, 103.02] over the six benchmarks — high at 1947 due to the near-singular A-matrix, normal range otherwise). S402 is a benchmark cross-section and per VAR-006 skips the chopped CSV / Extenbook pipeline. Note also that B is computed at producer prices, not unit quantities — the verbatim caveat is **"It is important to note that while there is enough information in standard (i.e. producer-price) input-output tables to calculate the purchaser price of aggregate inputs, outputs, and final demand components, there is not enough to calculate the purchaser price of individual commodities."** (ST 1994 Ch4 §4.1, p.80).</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>## Sources</t>
-        </is>
-      </c>
+      <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>## Sources</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>- KB chunks: `Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_10/full_transcription.md` (Ch4 §4.1, pp.78-83 — closed-form Leontief inverse, worked example); `chunk_27/full_transcription.md` (Appendix A — aggregation pipeline propagating into B)</t>
-        </is>
-      </c>
+      <c r="B39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>- Book tables: ST 1994 Table 4.2 (B-Matrix) at 85×85 producer-price level</t>
+          <t>- KB chunks: `Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_10/full_transcription.md` (Ch4 §4.1, pp.78-83 — closed-form Leontief inverse, worked example); `chunk_27/full_transcription.md` (Appendix A — aggregation pipeline propagating into B)</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>- External sources: BEA Benchmark Input-Output Accounts (1947, 1958, 1963, 1967, 1972, 1977) via S401 dependency</t>
+          <t>- Book tables: ST 1994 Table 4.2 (B-Matrix) at 85×85 producer-price level</t>
         </is>
       </c>
     </row>
@@ -890,39 +890,39 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>- Local files: derived in-pipeline from S401 outputs via `code/utils/io_matrix.py`; printed-book digitization at `data/source/book_tables/ch04/Table4_2_BMatrix.csv`</t>
+          <t>- External sources: BEA Benchmark Input-Output Accounts (1947, 1958, 1963, 1967, 1972, 1977) via S401 dependency</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>- Local files: derived in-pipeline from S401 outputs via `code/utils/io_matrix.py`; printed-book digitization at `data/source/book_tables/ch04/Table4_2_BMatrix.csv`</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>## Reference values</t>
-        </is>
-      </c>
+      <c r="B44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>## Reference values</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>- Six benchmark years matching S401: 1947, 1958, 1963, 1967, 1972, 1977</t>
-        </is>
-      </c>
+      <c r="B46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>- `b_frobenius_norm` range: `[10.47, 103.02]` — high at 1947 (near-singular A), normal otherwise</t>
+          <t>- Six benchmark years matching S401: 1947, 1958, 1963, 1967, 1972, 1977</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>- `b_trace ≥ n_sectors` at every year (mathematical guarantee from `B = I + A + A^2 + …`)</t>
+          <t>- `b_frobenius_norm` range: `[10.47, 103.02]` — high at 1947 (near-singular A), normal otherwise</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>- `(I - A)(I - A)^{-1} ≈ I` (leontief_max_dev &lt; 1e-9 at all benchmarks where A is well-conditioned)</t>
+          <t>- `b_trace ≥ n_sectors` at every year (mathematical guarantee from `B = I + A + A^2 + …`)</t>
         </is>
       </c>
     </row>
@@ -946,39 +946,39 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>- Worked numerical check from Ch4 Figure 4.3 p.83: with `app* = 1/5`, `hp* = 8/5`, `lambda* = 2 hr/$`</t>
+          <t>- `(I - A)(I - A)^{-1} ≈ I` (leontief_max_dev &lt; 1e-9 at all benchmarks where A is well-conditioned)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
-      <c r="B51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>- Worked numerical check from Ch4 Figure 4.3 p.83: with `app* = 1/5`, `hp* = 8/5`, `lambda* = 2 hr/$`</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>## Known issues</t>
-        </is>
-      </c>
+      <c r="B52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
-      <c r="B53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>## Known issues</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>- All approximation errors in S401's A-matrix (eating/drinking places, FAC scaling, g=0.25 ground rent) propagate into B through matrix inversion; the inversion can amplify near-singular behavior at 1947</t>
-        </is>
-      </c>
+      <c r="B54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>- Numerical stability at 1947 is the worst of the six benchmarks (Frobenius norm 103.02 vs. ~10-30 elsewhere) and is a documented S&amp;T issue, not a project artifact</t>
+          <t>- All approximation errors in S401's A-matrix (eating/drinking places, FAC scaling, g=0.25 ground rent) propagate into B through matrix inversion; the inversion can amplify near-singular behavior at 1947</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>- B is constructed at producer prices, not unit quantities, per the Ch4 §4.1 caveat — this matters when S701/S702 attempt to construct sector-disaggregated labor values</t>
+          <t>- Numerical stability at 1947 is the worst of the six benchmarks (Frobenius norm 103.02 vs. ~10-30 elsewhere) and is a documented S&amp;T issue, not a project artifact</t>
         </is>
       </c>
     </row>
@@ -994,7 +994,7 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>- No NAICS extension in the published spine (inherited from S401)</t>
+          <t>- B is constructed at producer prices, not unit quantities, per the Ch4 §4.1 caveat — this matters when S701/S702 attempt to construct sector-disaggregated labor values</t>
         </is>
       </c>
     </row>
@@ -1002,39 +1002,39 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>- The current Wave-1 S701/S702 implementation uses an aggregate scalar `mean(column_sum(B))` rather than `hp* · B`, which is a documented proxy (see S701/S702 DPRs); S402 itself is a faithful computation of B given S401's A</t>
+          <t>- No NAICS extension in the published spine (inherited from S401)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
-      <c r="B59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>- The current Wave-1 S701/S702 implementation uses an aggregate scalar `mean(column_sum(B))` rather than `hp* · B`, which is a documented proxy (see S701/S702 DPRs); S402 itself is a faithful computation of B given S401's A</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>## Cross-references</t>
-        </is>
-      </c>
+      <c r="B60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
-      <c r="B61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>## Cross-references</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>- Upstream: S401 (A-matrix — the only direct input)</t>
-        </is>
-      </c>
+      <c r="B62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>- Downstream: S701 (labor values, proxy), S702 (prices of production, proxy), S703 (value-price deviations, proxy) — all three currently substitute `mean(column_sum(B))` for the book's `hp* · B`</t>
+          <t>- Upstream: S401 (A-matrix — the only direct input)</t>
         </is>
       </c>
     </row>
@@ -1042,45 +1042,53 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>- Related external: any IO-based labor-value study (Wolff 1977a/b/1987; Sharpe 1982; Khanjian 1988/1989; Mohun 2005)</t>
+          <t>- Downstream: S701 (labor values, proxy), S702 (prices of production, proxy), S703 (value-price deviations, proxy) — all three currently substitute `mean(column_sum(B))` for the book's `hp* · B`</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
-      <c r="B65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>- Related external: any IO-based labor-value study (Wolff 1977a/b/1987; Sharpe 1982; Khanjian 1988/1989; Mohun 2005)</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>## Provenance trail</t>
-        </is>
-      </c>
+      <c r="B66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
-      <c r="B67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>## Provenance trail</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>- **Original research**: `Technical/research/S402_research.json`, researcher `agent`, 2026-05-06; ported from `ST2/research/T402_research.json` on 2026-05-14</t>
-        </is>
-      </c>
+      <c r="B68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>- **DPR enriched**: 2026-05-23 by Stage-3 cohort-1 ingestion agent (cohort agent 4); sources read = research JSON + KB chunks 10/27 cited via research JSON + registry entry</t>
+          <t>- **Original research**: `Technical/research/S402_research.json`, researcher `agent`, 2026-05-06; ported from `ST2/research/T402_research.json` on 2026-05-14</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
+        <is>
+          <t>- **DPR enriched**: 2026-05-23 by Stage-3 cohort-1 ingestion agent (cohort agent 4); sources read = research JSON + KB chunks 10/27 cited via research JSON + registry entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
         <is>
           <t>- **Anu Framework stage**: Stage 3 INGESTION (cohort 1, failing chapters); ingestion gate IDs P31/P32</t>
         </is>

--- a/extenbooks/S402.xlsx
+++ b/extenbooks/S402.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -483,7 +483,7 @@
         <v>1947</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>79.9427</v>
+        <v>2.6397</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>1958</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>32.0272</v>
+        <v>2.2522</v>
       </c>
     </row>
     <row r="5">
@@ -499,7 +499,7 @@
         <v>1963</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>32.6916</v>
+        <v>2.2299</v>
       </c>
     </row>
     <row r="6">
@@ -507,7 +507,7 @@
         <v>1967</v>
       </c>
       <c r="B6" s="3" t="n">
-        <v>10.4717</v>
+        <v>2.1618</v>
       </c>
     </row>
     <row r="7">
@@ -515,7 +515,7 @@
         <v>1972</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>103.0209</v>
+        <v>2.1818</v>
       </c>
     </row>
     <row r="8">
@@ -523,7 +523,47 @@
         <v>1977</v>
       </c>
       <c r="B8" s="3" t="n">
-        <v>98.9415</v>
+        <v>2.3242</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1997</v>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>1.9313</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>1.901</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>1.988</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>1.9788</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>1.9211</v>
       </c>
     </row>
   </sheetData>
@@ -636,7 +676,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1947-1977</t>
+          <t>1947-2017</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1601,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{"1947": 79.9427, "1958": 32.0272, "1963": 32.6916, "1967": 10.4717, "1972": 103.0209, "1977": 98.9415}</t>
+          <t>{"1947": 2.6397, "1958": 2.2522, "1963": 2.2299, "1967": 2.1618, "1972": 2.1818, "1977": 2.3242, "1997": 1.9313, "2002": 1.901, "2007": 1.988, "2012": 1.9788, "2017": 1.9211}</t>
         </is>
       </c>
     </row>
@@ -1573,7 +1613,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>[1.5, 3.5]</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S402.xlsx
+++ b/extenbooks/S402.xlsx
@@ -1114,7 +1114,7 @@
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>- **Original research**: `Technical/research/S402_research.json`, researcher `agent`, 2026-05-06; ported from `ST2/research/T402_research.json` on 2026-05-14</t>
+          <t>- **Original research**: `Technical/research/S402_research.json`, researcher `agent`, 2026-05-06; ported from `predecessor-build/research/T402_research.json` on 2026-05-14</t>
         </is>
       </c>
     </row>
